--- a/Result/profitability/3191.xlsx
+++ b/Result/profitability/3191.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06625</v>
+        <v>-0.04125</v>
       </c>
       <c r="N2" t="n">
-        <v>22.66375</v>
+        <v>22.9325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.09999999999999999</v>
+        <v>-0.07999999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>20.195</v>
+        <v>20.62375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05249999999999999</v>
+        <v>-0.03999999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>19.25</v>
+        <v>19.61125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.13</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.18875</v>
+        <v>-0.11875</v>
       </c>
       <c r="N5" t="n">
-        <v>13.39375</v>
+        <v>14.26875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1175</v>
+        <v>-0.24625</v>
       </c>
       <c r="N6" t="n">
-        <v>12.415</v>
+        <v>12.99</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.29625</v>
+        <v>-0.2837499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>11.27125</v>
+        <v>10.9475</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.33125</v>
+        <v>-0.28375</v>
       </c>
       <c r="N8" t="n">
-        <v>9.022500000000001</v>
+        <v>8.688750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-0.28375</v>
       </c>
       <c r="N9" t="n">
-        <v>7.433750000000002</v>
+        <v>7.433750000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>48</v>
+      </c>
+      <c r="D75" t="n">
+        <v>35</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.001250000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.98875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.1875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.670000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09047780413419182</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3528225806451613</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
